--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486937_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486937_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>S. MERLO</t>
+          <t>N. REID</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.5174</v>
+        <v>6.1696</v>
       </c>
       <c r="E2" t="n">
-        <v>2.8125</v>
+        <v>4.4252</v>
       </c>
       <c r="F2" t="n">
-        <v>2.7049</v>
+        <v>1.7443</v>
       </c>
       <c r="G2" t="n">
-        <v>5.0066</v>
+        <v>4.1569</v>
       </c>
       <c r="H2" t="n">
-        <v>1.823</v>
+        <v>-0.9055</v>
       </c>
       <c r="I2" t="n">
-        <v>3.1837</v>
+        <v>5.0623</v>
       </c>
       <c r="J2" t="n">
-        <v>3.3852</v>
+        <v>4.495</v>
       </c>
       <c r="K2" t="n">
-        <v>1.5962</v>
+        <v>0.0618</v>
       </c>
       <c r="L2" t="n">
-        <v>1.789</v>
+        <v>4.4332</v>
       </c>
       <c r="M2" t="n">
-        <v>1.6215</v>
+        <v>-0.3381</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2268</v>
+        <v>-0.9673</v>
       </c>
       <c r="O2" t="n">
-        <v>1.3947</v>
+        <v>0.6291</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.4107</v>
+        <v>1.4374</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.0267</v>
+        <v>-0.2053</v>
       </c>
       <c r="R2" t="n">
-        <v>0.616</v>
+        <v>1.6427</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.2571</v>
+        <v>-0.6032999999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.7246</v>
+        <v>-0.3449</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4674</v>
+        <v>-0.2584</v>
       </c>
       <c r="V2" t="n">
         <v>1.1786</v>
       </c>
       <c r="W2" t="n">
-        <v>1.1786</v>
+        <v>0.4805</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>0.6982</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>N. REID</t>
+          <t>S. MERLO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.4507</v>
+        <v>5.8173</v>
       </c>
       <c r="E3" t="n">
-        <v>3.9138</v>
+        <v>3.2309</v>
       </c>
       <c r="F3" t="n">
-        <v>1.5368</v>
+        <v>2.5864</v>
       </c>
       <c r="G3" t="n">
-        <v>4.1569</v>
+        <v>5.0066</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.9055</v>
+        <v>1.823</v>
       </c>
       <c r="I3" t="n">
-        <v>5.0623</v>
+        <v>3.1837</v>
       </c>
       <c r="J3" t="n">
-        <v>4.495</v>
+        <v>3.3852</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0618</v>
+        <v>1.5962</v>
       </c>
       <c r="L3" t="n">
-        <v>4.4332</v>
+        <v>1.789</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.3381</v>
+        <v>1.6215</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.9673</v>
+        <v>0.2268</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6291</v>
+        <v>1.3947</v>
       </c>
       <c r="P3" t="n">
-        <v>1.4374</v>
+        <v>-0.4107</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.2053</v>
+        <v>-1.0267</v>
       </c>
       <c r="R3" t="n">
-        <v>1.6427</v>
+        <v>0.616</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.3222</v>
+        <v>0.0427</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8563</v>
+        <v>-0.3062</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4659</v>
+        <v>0.3489</v>
       </c>
       <c r="V3" t="n">
         <v>1.1786</v>
       </c>
       <c r="W3" t="n">
-        <v>0.4805</v>
+        <v>1.1786</v>
       </c>
       <c r="X3" t="n">
-        <v>0.6982</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.0212</v>
+        <v>5.0591</v>
       </c>
       <c r="E4" t="n">
-        <v>1.9311</v>
+        <v>2.2062</v>
       </c>
       <c r="F4" t="n">
-        <v>3.0901</v>
+        <v>2.853</v>
       </c>
       <c r="G4" t="n">
         <v>2.5906</v>
@@ -766,13 +766,13 @@
         <v>2.0534</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2122</v>
+        <v>-0.1742</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.9881</v>
+        <v>-0.713</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7759</v>
+        <v>0.5387999999999999</v>
       </c>
       <c r="V4" t="n">
         <v>0.5893</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>B. VANACLOCHA SANCHEZ</t>
+          <t>V. AGUILAR HERNANDEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.1878</v>
+        <v>4.2639</v>
       </c>
       <c r="E5" t="n">
-        <v>2.9492</v>
+        <v>3.7394</v>
       </c>
       <c r="F5" t="n">
-        <v>1.2386</v>
+        <v>0.5245</v>
       </c>
       <c r="G5" t="n">
-        <v>2.684</v>
+        <v>3.9946</v>
       </c>
       <c r="H5" t="n">
-        <v>1.0736</v>
+        <v>2.2056</v>
       </c>
       <c r="I5" t="n">
-        <v>1.6104</v>
+        <v>1.789</v>
       </c>
       <c r="J5" t="n">
-        <v>2.0151</v>
+        <v>3.9672</v>
       </c>
       <c r="K5" t="n">
-        <v>1.2653</v>
+        <v>2.7836</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7498</v>
+        <v>1.1836</v>
       </c>
       <c r="M5" t="n">
-        <v>0.6689000000000001</v>
+        <v>0.0274</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1917</v>
+        <v>-0.578</v>
       </c>
       <c r="O5" t="n">
-        <v>0.8606</v>
+        <v>0.6054</v>
       </c>
       <c r="P5" t="n">
-        <v>0.616</v>
+        <v>-0.616</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.2321</v>
       </c>
       <c r="R5" t="n">
         <v>0.616</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0581</v>
+        <v>-0.2934</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1045</v>
+        <v>-0.1744</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0464</v>
+        <v>-0.1189</v>
       </c>
       <c r="V5" t="n">
-        <v>0.8295</v>
+        <v>1.1786</v>
       </c>
       <c r="W5" t="n">
-        <v>0.8295</v>
+        <v>1.1786</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. HIERREZUELO SERER</t>
+          <t>B. VANACLOCHA SANCHEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.7942</v>
+        <v>3.7694</v>
       </c>
       <c r="E6" t="n">
-        <v>2.3034</v>
+        <v>2.5308</v>
       </c>
       <c r="F6" t="n">
-        <v>1.4909</v>
+        <v>1.2386</v>
       </c>
       <c r="G6" t="n">
-        <v>2.5749</v>
+        <v>2.684</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4441</v>
+        <v>1.0736</v>
       </c>
       <c r="I6" t="n">
-        <v>2.1308</v>
+        <v>1.6104</v>
       </c>
       <c r="J6" t="n">
-        <v>2.1872</v>
+        <v>2.0151</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6618000000000001</v>
+        <v>1.2653</v>
       </c>
       <c r="L6" t="n">
-        <v>1.5254</v>
+        <v>0.7498</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3876</v>
+        <v>0.6689000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2177</v>
+        <v>-0.1917</v>
       </c>
       <c r="O6" t="n">
-        <v>0.6054</v>
+        <v>0.8606</v>
       </c>
       <c r="P6" t="n">
-        <v>0.4107</v>
+        <v>0.616</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.2053</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0.616</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3282</v>
+        <v>-0.3603</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.159</v>
+        <v>-0.3139</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4872</v>
+        <v>-0.0464</v>
       </c>
       <c r="V6" t="n">
-        <v>0.4805</v>
+        <v>0.8295</v>
       </c>
       <c r="W6" t="n">
-        <v>0.4805</v>
+        <v>0.8295</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>V. AGUILAR HERNANDEZ</t>
+          <t>J. HIERREZUELO SERER</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>3.7433</v>
+        <v>3.7325</v>
       </c>
       <c r="E7" t="n">
-        <v>3.1892</v>
+        <v>2.3305</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5541</v>
+        <v>1.4019</v>
       </c>
       <c r="G7" t="n">
-        <v>3.9946</v>
+        <v>2.5749</v>
       </c>
       <c r="H7" t="n">
-        <v>2.2056</v>
+        <v>0.4441</v>
       </c>
       <c r="I7" t="n">
-        <v>1.789</v>
+        <v>2.1308</v>
       </c>
       <c r="J7" t="n">
-        <v>3.9672</v>
+        <v>2.1872</v>
       </c>
       <c r="K7" t="n">
-        <v>2.7836</v>
+        <v>0.6618000000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>1.1836</v>
+        <v>1.5254</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0274</v>
+        <v>0.3876</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.578</v>
+        <v>-0.2177</v>
       </c>
       <c r="O7" t="n">
         <v>0.6054</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.616</v>
+        <v>0.4107</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.2321</v>
+        <v>-0.2053</v>
       </c>
       <c r="R7" t="n">
         <v>0.616</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.8139</v>
+        <v>0.2664</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.7246</v>
+        <v>-0.1318</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0893</v>
+        <v>0.3983</v>
       </c>
       <c r="V7" t="n">
-        <v>1.1786</v>
+        <v>0.4805</v>
       </c>
       <c r="W7" t="n">
-        <v>1.1786</v>
+        <v>0.4805</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>V. MUÑOZ QUIÑONES</t>
+          <t>A. VERA PICAZO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>3.0555</v>
+        <v>2.655</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2747</v>
+        <v>1.7507</v>
       </c>
       <c r="F8" t="n">
-        <v>2.7808</v>
+        <v>0.9043</v>
       </c>
       <c r="G8" t="n">
-        <v>2.004</v>
+        <v>2.0976</v>
       </c>
       <c r="H8" t="n">
-        <v>1.7776</v>
+        <v>1.0899</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2264</v>
+        <v>1.0077</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8639</v>
+        <v>1.2079</v>
       </c>
       <c r="K8" t="n">
-        <v>1.5217</v>
+        <v>0.6424</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6579</v>
+        <v>0.5656</v>
       </c>
       <c r="M8" t="n">
-        <v>1.1402</v>
+        <v>0.8897</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2559</v>
+        <v>0.4475</v>
       </c>
       <c r="O8" t="n">
-        <v>0.8843</v>
+        <v>0.4422</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.8214</v>
+        <v>0.4107</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.2588</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.4374</v>
+        <v>0.4107</v>
       </c>
       <c r="S8" t="n">
-        <v>2.3533</v>
+        <v>-0.4426</v>
       </c>
       <c r="T8" t="n">
-        <v>1.6696</v>
+        <v>-0.527</v>
       </c>
       <c r="U8" t="n">
-        <v>0.6837</v>
+        <v>0.0844</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.4805</v>
+        <v>0.5893</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.0698</v>
       </c>
       <c r="X8" t="n">
         <v>-0.4805</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>O. BRAMBLE</t>
+          <t>A. GARCIA BORREGO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,40 +1111,40 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>2.5699</v>
+        <v>2.3845</v>
       </c>
       <c r="E9" t="n">
-        <v>0.09229999999999999</v>
+        <v>0.1535</v>
       </c>
       <c r="F9" t="n">
-        <v>2.4777</v>
+        <v>2.231</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8829</v>
+        <v>-0.0658</v>
       </c>
       <c r="H9" t="n">
-        <v>1.1354</v>
+        <v>-0.3895</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2525</v>
+        <v>0.3238</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.3385</v>
+        <v>-0.3982</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2404</v>
+        <v>0.0229</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.579</v>
+        <v>-0.4211</v>
       </c>
       <c r="M9" t="n">
-        <v>1.2215</v>
+        <v>0.3325</v>
       </c>
       <c r="N9" t="n">
-        <v>0.895</v>
+        <v>-0.4124</v>
       </c>
       <c r="O9" t="n">
-        <v>0.3264</v>
+        <v>0.7449</v>
       </c>
       <c r="P9" t="n">
         <v>0.4107</v>
@@ -1156,19 +1156,19 @@
         <v>1.4374</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0977</v>
+        <v>-0.0775</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0386</v>
+        <v>-0.7789</v>
       </c>
       <c r="U9" t="n">
-        <v>0.059</v>
+        <v>0.7014</v>
       </c>
       <c r="V9" t="n">
-        <v>1.1786</v>
+        <v>2.117</v>
       </c>
       <c r="W9" t="n">
-        <v>1.4189</v>
+        <v>2.3573</v>
       </c>
       <c r="X9" t="n">
         <v>-0.2402</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. VERA PICAZO</t>
+          <t>O. BRAMBLE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>2.5068</v>
+        <v>2.3813</v>
       </c>
       <c r="E10" t="n">
-        <v>1.7507</v>
+        <v>-0.1557</v>
       </c>
       <c r="F10" t="n">
-        <v>0.756</v>
+        <v>2.5369</v>
       </c>
       <c r="G10" t="n">
-        <v>2.0976</v>
+        <v>0.8829</v>
       </c>
       <c r="H10" t="n">
-        <v>1.0899</v>
+        <v>1.1354</v>
       </c>
       <c r="I10" t="n">
-        <v>1.0077</v>
+        <v>-0.2525</v>
       </c>
       <c r="J10" t="n">
-        <v>1.2079</v>
+        <v>-0.3385</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6424</v>
+        <v>0.2404</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5656</v>
+        <v>-0.579</v>
       </c>
       <c r="M10" t="n">
-        <v>0.8897</v>
+        <v>1.2215</v>
       </c>
       <c r="N10" t="n">
-        <v>0.4475</v>
+        <v>0.895</v>
       </c>
       <c r="O10" t="n">
-        <v>0.4422</v>
+        <v>0.3264</v>
       </c>
       <c r="P10" t="n">
         <v>0.4107</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-1.0267</v>
       </c>
       <c r="R10" t="n">
-        <v>0.4107</v>
+        <v>1.4374</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5908</v>
+        <v>-0.091</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.527</v>
+        <v>-0.2093</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0638</v>
+        <v>0.1183</v>
       </c>
       <c r="V10" t="n">
-        <v>0.5893</v>
+        <v>1.1786</v>
       </c>
       <c r="W10" t="n">
-        <v>1.0698</v>
+        <v>1.4189</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.4805</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. GARCIA BORREGO</t>
+          <t>V. MUÑOZ QUIÑONES</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>1.7537</v>
+        <v>1.6108</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.1216</v>
+        <v>-0.9921</v>
       </c>
       <c r="F11" t="n">
-        <v>1.8753</v>
+        <v>2.6029</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.0658</v>
+        <v>2.004</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.3895</v>
+        <v>1.7776</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3238</v>
+        <v>0.2264</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.3982</v>
+        <v>0.8639</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0229</v>
+        <v>1.5217</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.4211</v>
+        <v>-0.6579</v>
       </c>
       <c r="M11" t="n">
-        <v>0.3325</v>
+        <v>1.1402</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.4124</v>
+        <v>0.2559</v>
       </c>
       <c r="O11" t="n">
-        <v>0.7449</v>
+        <v>0.8843</v>
       </c>
       <c r="P11" t="n">
-        <v>0.4107</v>
+        <v>-0.8214</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.0267</v>
+        <v>-2.2588</v>
       </c>
       <c r="R11" t="n">
         <v>1.4374</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7082000000000001</v>
+        <v>0.9086</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.054</v>
+        <v>0.4028</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3457</v>
+        <v>0.5058</v>
       </c>
       <c r="V11" t="n">
-        <v>2.117</v>
+        <v>-0.4805</v>
       </c>
       <c r="W11" t="n">
-        <v>2.3573</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.2402</v>
+        <v>-0.4805</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4484</v>
+        <v>1.1938</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.9634</v>
+        <v>-1.0994</v>
       </c>
       <c r="F12" t="n">
-        <v>2.4118</v>
+        <v>2.2932</v>
       </c>
       <c r="G12" t="n">
         <v>-1.2051</v>
@@ -1390,13 +1390,13 @@
         <v>1.4374</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.8885999999999999</v>
+        <v>-0.1432</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.1198</v>
+        <v>-0.2559</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2312</v>
+        <v>0.1126</v>
       </c>
       <c r="V12" t="n">
         <v>1.31</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>38.0489</v>
+        <v>39.0372</v>
       </c>
       <c r="E13" t="n">
-        <v>17.1319</v>
+        <v>18.12</v>
       </c>
       <c r="F13" t="n">
         <v>20.917</v>
@@ -1447,7 +1447,7 @@
         <v>9.2964</v>
       </c>
       <c r="L13" t="n">
-        <v>7.640300000000002</v>
+        <v>7.6403</v>
       </c>
       <c r="M13" t="n">
         <v>7.7847</v>
@@ -1456,7 +1456,7 @@
         <v>-0.3613999999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>8.146000000000001</v>
+        <v>8.145999999999999</v>
       </c>
       <c r="P13" t="n">
         <v>5.133599999999999</v>
@@ -1468,13 +1468,13 @@
         <v>12.3204</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.9557</v>
+        <v>-0.9677999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>-4.3407</v>
+        <v>-3.3525</v>
       </c>
       <c r="U13" t="n">
-        <v>2.3847</v>
+        <v>2.3848</v>
       </c>
       <c r="V13" t="n">
         <v>10.1495</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.2184</v>
+        <v>1.0982</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.1234</v>
+        <v>-0.3326</v>
       </c>
       <c r="F14" t="n">
-        <v>1.3418</v>
+        <v>1.4307</v>
       </c>
       <c r="G14" t="n">
         <v>0.912</v>
@@ -1546,13 +1546,13 @@
         <v>0.616</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1483</v>
+        <v>0.0281</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0386</v>
+        <v>-0.1706</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1097</v>
+        <v>0.1986</v>
       </c>
       <c r="V14" t="n">
         <v>-0.4579</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. KNOWLES</t>
+          <t>O. OKENCHI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4248</v>
+        <v>-0.4157</v>
       </c>
       <c r="E15" t="n">
-        <v>2.6635</v>
+        <v>0.0192</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.2387</v>
+        <v>-0.4349</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.0016</v>
+        <v>-0.2491</v>
       </c>
       <c r="H15" t="n">
-        <v>2.4238</v>
+        <v>-0.2886</v>
       </c>
       <c r="I15" t="n">
-        <v>-2.4254</v>
+        <v>0.0395</v>
       </c>
       <c r="J15" t="n">
-        <v>3.8071</v>
+        <v>-0.0544</v>
       </c>
       <c r="K15" t="n">
-        <v>3.7282</v>
+        <v>-0.0939</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0789</v>
+        <v>0.0395</v>
       </c>
       <c r="M15" t="n">
-        <v>-3.8088</v>
+        <v>-0.1947</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.3044</v>
+        <v>-0.1947</v>
       </c>
       <c r="O15" t="n">
-        <v>-2.5044</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.4374</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.2588</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.8214</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.2129</v>
+        <v>0.0736</v>
       </c>
       <c r="T15" t="n">
-        <v>1.2239</v>
+        <v>0.0736</v>
       </c>
       <c r="U15" t="n">
-        <v>0.989</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.3491</v>
+        <v>-0.2402</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.1088</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
         <v>-0.2402</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>O. OKENCHI</t>
+          <t>D. KNOWLES</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.4157</v>
+        <v>-0.963</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0192</v>
+        <v>1.5128</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.4349</v>
+        <v>-2.4758</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.2491</v>
+        <v>-0.0016</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.2886</v>
+        <v>2.4238</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0395</v>
+        <v>-2.4254</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.0544</v>
+        <v>3.8071</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.0939</v>
+        <v>3.7282</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0395</v>
+        <v>0.0789</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.1947</v>
+        <v>-3.8088</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1947</v>
+        <v>-1.3044</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>-2.5044</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>-1.4374</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-2.2588</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>0.8214</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0736</v>
+        <v>0.8250999999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0736</v>
+        <v>0.0733</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>0.7518</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.2402</v>
+        <v>-0.3491</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>-0.1088</v>
       </c>
       <c r="X16" t="n">
         <v>-0.2402</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.5538</v>
+        <v>-1.9426</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.2587</v>
+        <v>-1.6771</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2951</v>
+        <v>-0.2655</v>
       </c>
       <c r="G17" t="n">
         <v>-0.6389</v>
@@ -1780,13 +1780,13 @@
         <v>0.4107</v>
       </c>
       <c r="S17" t="n">
-        <v>0.8798</v>
+        <v>0.491</v>
       </c>
       <c r="T17" t="n">
-        <v>0.08500000000000001</v>
+        <v>-0.3334</v>
       </c>
       <c r="U17" t="n">
-        <v>0.7948</v>
+        <v>0.8244</v>
       </c>
       <c r="V17" t="n">
         <v>-1.1786</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.7644</v>
+        <v>-2.4812</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.6736</v>
+        <v>-0.6276</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.0907</v>
+        <v>-1.8536</v>
       </c>
       <c r="G18" t="n">
         <v>-2.3644</v>
@@ -1858,13 +1858,13 @@
         <v>1.4374</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.322</v>
+        <v>-0.0388</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.4996</v>
+        <v>-0.4536</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1776</v>
+        <v>0.4147</v>
       </c>
       <c r="V18" t="n">
         <v>-1.31</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-4.9809</v>
+        <v>-5.0978</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.7137</v>
+        <v>-2.5045</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.2672</v>
+        <v>-2.5933</v>
       </c>
       <c r="G19" t="n">
         <v>-5.5345</v>
@@ -1936,13 +1936,13 @@
         <v>1.2321</v>
       </c>
       <c r="S19" t="n">
-        <v>0.5536</v>
+        <v>0.4367</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4265</v>
+        <v>-0.2173</v>
       </c>
       <c r="U19" t="n">
-        <v>0.9801</v>
+        <v>0.654</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-5.5322</v>
+        <v>-5.7275</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.3944</v>
+        <v>-0.7083</v>
       </c>
       <c r="F20" t="n">
-        <v>-5.1378</v>
+        <v>-5.0192</v>
       </c>
       <c r="G20" t="n">
         <v>-2.188</v>
@@ -2014,13 +2014,13 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.323</v>
+        <v>0.1278</v>
       </c>
       <c r="T20" t="n">
-        <v>0.244</v>
+        <v>-0.0698</v>
       </c>
       <c r="U20" t="n">
-        <v>0.079</v>
+        <v>0.1976</v>
       </c>
       <c r="V20" t="n">
         <v>-3.6673</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.8725</v>
+        <v>-6.2142</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.8847</v>
+        <v>-4.9893</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.9878</v>
+        <v>-1.2249</v>
       </c>
       <c r="G21" t="n">
         <v>-4.7233</v>
@@ -2092,13 +2092,13 @@
         <v>1.2321</v>
       </c>
       <c r="S21" t="n">
-        <v>0.7523</v>
+        <v>0.4106</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2366</v>
+        <v>-0.3412</v>
       </c>
       <c r="U21" t="n">
-        <v>0.989</v>
+        <v>0.7518</v>
       </c>
       <c r="V21" t="n">
         <v>1.1786</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.7471</v>
+        <v>-6.5535</v>
       </c>
       <c r="E22" t="n">
-        <v>-7.0634</v>
+        <v>-6.9588</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3163</v>
+        <v>0.4052</v>
       </c>
       <c r="G22" t="n">
         <v>-3.0892</v>
@@ -2170,13 +2170,13 @@
         <v>0.616</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1383</v>
+        <v>0.0552</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7169</v>
+        <v>-0.6123</v>
       </c>
       <c r="U22" t="n">
-        <v>0.5785</v>
+        <v>0.6675</v>
       </c>
       <c r="V22" t="n">
         <v>-1.8768</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-10.8255</v>
+        <v>-9.7515</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.4877</v>
+        <v>-4.6509</v>
       </c>
       <c r="F23" t="n">
-        <v>-5.3377</v>
+        <v>-5.1006</v>
       </c>
       <c r="G23" t="n">
         <v>-6.8444</v>
@@ -2248,13 +2248,13 @@
         <v>0.8214</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.5273</v>
+        <v>-0.4534</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.1702</v>
+        <v>-0.3334</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3571</v>
+        <v>-0.12</v>
       </c>
       <c r="V23" t="n">
         <v>-2.2484</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-38.0489</v>
+        <v>-38.0488</v>
       </c>
       <c r="E24" t="n">
-        <v>-20.9169</v>
+        <v>-20.9171</v>
       </c>
       <c r="F24" t="n">
-        <v>-17.1318</v>
+        <v>-17.1319</v>
       </c>
       <c r="G24" t="n">
         <v>-24.7214</v>
@@ -2299,7 +2299,7 @@
         <v>-15.7862</v>
       </c>
       <c r="J24" t="n">
-        <v>-7.784600000000001</v>
+        <v>-7.784599999999999</v>
       </c>
       <c r="K24" t="n">
         <v>0.3613000000000008</v>
@@ -2317,7 +2317,7 @@
         <v>-7.6404</v>
       </c>
       <c r="P24" t="n">
-        <v>-5.133400000000001</v>
+        <v>-5.1334</v>
       </c>
       <c r="Q24" t="n">
         <v>-12.3206</v>
@@ -2326,13 +2326,13 @@
         <v>7.1871</v>
       </c>
       <c r="S24" t="n">
-        <v>1.955899999999999</v>
+        <v>1.9559</v>
       </c>
       <c r="T24" t="n">
         <v>-2.3847</v>
       </c>
       <c r="U24" t="n">
-        <v>4.340599999999999</v>
+        <v>4.3404</v>
       </c>
       <c r="V24" t="n">
         <v>-10.1497</v>
